--- a/BWI/bestwine_output/bestwine_Paraguay.xlsx
+++ b/BWI/bestwine_output/bestwine_Paraguay.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA77"/>
+  <dimension ref="A1:AA79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -9045,6 +9045,232 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Cervepar Sa</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Cervepar Sa</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>117814</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>721 Avenida Brasilia</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>001410</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://cervepar.com.py</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>contacto@cervepar.com.py</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 729 7500</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>80003457-0</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cervepar/</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Cervepar/</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cervepar</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@cervepar3265</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo Alvarenga</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>Procurement Leader</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr"/>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rodrigo-alvarenga-30a093186/</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Cervepar Sa</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Cervepar Sa</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>117814</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Asunción</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>721 Avenida Brasilia</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>001410</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>https://cervepar.com.py</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>contacto@cervepar.com.py</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>+595 21 729 7500</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>1910</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>80003457-0</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cervepar/</t>
+        </is>
+      </c>
+      <c r="S79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Cervepar/</t>
+        </is>
+      </c>
+      <c r="T79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cervepar</t>
+        </is>
+      </c>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@cervepar3265</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>Calixto Ramirez</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>Area Manager</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr"/>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/calixto-ramirez-b2b26ba0/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
